--- a/TAZA/_документы/Бюджет ТАЗА – вариант Лазурный.xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – вариант Лазурный.xlsx
@@ -128,7 +128,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="566">
   <si>
     <t>Бюджет проектного офиса «Таза Қазақстан» (ЦАКФ) на октябрь–декабрь 2026 и 2027 год — СВОД, ₸</t>
   </si>
@@ -142,12 +142,6 @@
     <t>В среднем в месяц 2027</t>
   </si>
   <si>
-    <t>Штатная численность, чел.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  из них нанять (новые позиции), чел.</t>
-  </si>
-  <si>
     <t>4. ДМС и ОСНС штатных сотрудников</t>
   </si>
   <si>
@@ -1714,9 +1708,6 @@
     <t>оценка; уточнить после осмотра помещений (БЦ «Лазурный», 6 этаж)</t>
   </si>
   <si>
-    <t>Проект от 10.10.2026 (v15-2). Штат — по структуре и штатке 01.10.2026: 30 человек (Фонд с экспертной группой — 9, проектный офис — 21); с 21.10.2026 — 18, с 01.2027 — 1 (Ахантаева), с 02.2027 — 11 (в т.ч. экспертная группа и Абулхан); аутсорс — 7 позиций, расчёт — на листе «Аутсорс», в бюджете. Аренда – вариант 2: БЦ «Лазурный», ул. Сарайшык, 7/7, 6 этаж целиком: 469,3 м² полезной по обмерному плану; к оплате 657,1 м² (коэффициент общих зон 1,4); коммунальные, клининг и охрана – в ставке; 5 парковочных мест на этаж; в 2026 – с 21.10. Проекты и мероприятия — по статьям проектного офиса, однотипные объединены, — на листе «Проекты (вне бюджета)», в ИТОГО не входят. В оснащении — ламинатор, переплётчик, сетевые фильтры, удлинители, кабель-канал, стойка для ТВ, источники бесперебойного питания (10 шт.). Суммы пересчитываются от листов «Параметры», «Штат», «Командировки», «Оснащение и офис», «Канцелярия», «Смета фото-видео».</t>
-  </si>
-  <si>
     <t>6. Оснащение (разово): ноутбуки, мебель и стеллажи с их сборкой, МФУ А3 и 2 МФУ А4, ламинатор и переплётчик, удлинители (сетевые фильтры), ИБП (10 шт.), фото-видео, сеть</t>
   </si>
   <si>
@@ -1829,6 +1820,12 @@
   </si>
   <si>
     <t>Разница (2 – 1)</t>
+  </si>
+  <si>
+    <t>Штатная численность на конец периода, чел.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  из них нанять в периоде (новые позиции), чел.</t>
   </si>
 </sst>
 </file>
@@ -2077,7 +2074,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2276,6 +2273,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2541,7 +2541,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="72.7109375" style="4" customWidth="1"/>
@@ -2555,789 +2555,796 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C3" s="43">
         <v>2027</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>3</v>
       </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="B4" s="4">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=3")</f>
+        <v>18</v>
+      </c>
+      <c r="C4" s="4">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!I5:I41,"&lt;=15")</f>
+        <v>30</v>
+      </c>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="B5" s="4">
-        <f>SUMIF(Штат!E5:E41,"штат",Штат!G5:G41)</f>
-        <v>30</v>
-      </c>
-      <c r="C5" s="4">
-        <f>B5</f>
-        <v>30</v>
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&lt;=3")</f>
+        <v>14</v>
+      </c>
+      <c r="C5" s="83">
+        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая",Штат!I5:I41,"&gt;3")</f>
+        <v>12</v>
       </c>
       <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>5</v>
+        <v>327</v>
       </c>
       <c r="B6" s="4">
-        <f>SUMIFS(Штат!G5:G41,Штат!E5:E41,"штат",Штат!F5:F41,"новая")</f>
-        <v>26</v>
-      </c>
-      <c r="D6" s="48"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="4">
+        <f>SUMPRODUCT((Штат!I8:I13&lt;=3)*Штат!G8:G13)+SUMPRODUCT((Штат!E17:E36="штат")*(Штат!I17:I36&lt;=3)*Штат!G17:G36)</f>
+        <v>12</v>
+      </c>
+      <c r="C6" s="4">
         <f>Штат!G43</f>
         <v>21</v>
       </c>
-      <c r="C7" s="4">
-        <f>B7</f>
-        <v>21</v>
-      </c>
-      <c r="D7" s="48"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B8" s="49">
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="49">
         <f>SUMIFS(Штат!N5:N41,Штат!E5:E41,"штат")</f>
         <v>58691747.741935484</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C7" s="49">
         <f>SUMIFS(Штат!O5:O41,Штат!E5:E41,"штат")</f>
         <v>419273990</v>
       </c>
+      <c r="D7" s="50">
+        <f>C7/12</f>
+        <v>34939499.166666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" s="49">
+        <f>Аутсорс!K11</f>
+        <v>15843354.83870968</v>
+      </c>
+      <c r="C8" s="49">
+        <f>Аутсорс!L11</f>
+        <v>80736000</v>
+      </c>
       <c r="D8" s="50">
         <f>C8/12</f>
-        <v>34939499.166666664</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>6728000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="B9" s="49">
-        <f>Аутсорс!K11</f>
-        <v>15843354.83870968</v>
+        <f>Штат!P42</f>
+        <v>23115060</v>
       </c>
       <c r="C9" s="49">
-        <f>Аутсорс!L11</f>
-        <v>80736000</v>
+        <f>Штат!Q42</f>
+        <v>139757996.66666666</v>
       </c>
       <c r="D9" s="50">
         <f>C9/12</f>
-        <v>6728000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>11646499.722222222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>418</v>
+        <v>4</v>
       </c>
       <c r="B10" s="49">
-        <f>Штат!P42</f>
-        <v>23115060</v>
+        <f>Штат!R42</f>
+        <v>854387.09677419392</v>
       </c>
       <c r="C10" s="49">
-        <f>Штат!Q42</f>
-        <v>139757996.66666666</v>
+        <f>Штат!S42</f>
+        <v>6631000</v>
       </c>
       <c r="D10" s="50">
         <f>C10/12</f>
-        <v>11646499.722222222</v>
+        <v>552583.33333333337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="49">
-        <f>Штат!R42</f>
-        <v>854387.09677419392</v>
+        <f>Командировки!I26</f>
+        <v>7246775.9408602165</v>
       </c>
       <c r="C11" s="49">
-        <f>Штат!S42</f>
-        <v>6631000</v>
+        <f>Командировки!J26</f>
+        <v>37657517.125</v>
       </c>
       <c r="D11" s="50">
         <f>C11/12</f>
-        <v>552583.33333333337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3138126.4270833335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>526</v>
       </c>
       <c r="B12" s="49">
-        <f>Командировки!I26</f>
-        <v>7246775.9408602165</v>
-      </c>
-      <c r="C12" s="49">
-        <f>Командировки!J26</f>
-        <v>37657517.125</v>
-      </c>
-      <c r="D12" s="50">
-        <f>C12/12</f>
-        <v>3138126.4270833335</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B13" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
         <v>41946058</v>
       </c>
-      <c r="C13" s="49">
+      <c r="C12" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Оснащение")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="50"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="49">
+      <c r="D12" s="50"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Офис")</f>
         <v>38573211.290322587</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C13" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Офис")</f>
         <v>128303400</v>
       </c>
-      <c r="D14" s="50">
-        <f>C14/12</f>
+      <c r="D13" s="50">
+        <f>C13/12</f>
         <v>10691950</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B15" s="51">
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B14" s="51">
         <f>'Оснащение и офис'!I39</f>
         <v>23209761.290322583</v>
       </c>
-      <c r="C15" s="51">
+      <c r="C14" s="51">
         <f>'Оснащение и офис'!J39</f>
         <v>118274400</v>
       </c>
-      <c r="D15" s="51">
-        <f>C15/12</f>
+      <c r="D14" s="51">
+        <f>C14/12</f>
         <v>9856200</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B16" s="51">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="51">
         <f>'Оснащение и офис'!I40</f>
         <v>9856200</v>
       </c>
-      <c r="C16" s="51">
+      <c r="C15" s="51">
         <f>'Оснащение и офис'!J40</f>
         <v>0</v>
       </c>
-      <c r="D16" s="51"/>
+      <c r="D15" s="51"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B16" s="49">
+        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
+        <v>820500</v>
+      </c>
+      <c r="C16" s="49">
+        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
+        <v>9282000</v>
+      </c>
+      <c r="D16" s="50">
+        <f t="shared" ref="D16:D24" si="0">C16/12</f>
+        <v>773500</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>502</v>
+        <v>366</v>
       </c>
       <c r="B17" s="49">
-        <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
-        <v>820500</v>
-      </c>
-      <c r="C17" s="49">
-        <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Цифровые")</f>
-        <v>9282000</v>
-      </c>
-      <c r="D17" s="50">
-        <f t="shared" ref="D17:D25" si="0">C17/12</f>
-        <v>773500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B18" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>3325000</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C17" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Медиа")</f>
         <v>25300000</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D17" s="50">
         <f t="shared" si="0"/>
         <v>2108333.3333333335</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
-        <v>477</v>
-      </c>
-      <c r="B19" s="52">
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="B18" s="52">
         <f>'Проекты (вне бюджета)'!G16</f>
         <v>213000000</v>
       </c>
-      <c r="C19" s="52">
+      <c r="C18" s="52">
         <f>'Проекты (вне бюджета)'!H16</f>
         <v>1530000000</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D18" s="53">
         <f t="shared" si="0"/>
         <v>127500000</v>
       </c>
-      <c r="E19" s="46" t="s">
-        <v>419</v>
-      </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="49">
+      <c r="E18" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="49">
         <f>SUMIFS('Оснащение и офис'!I5:I181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>5300000</v>
       </c>
-      <c r="C20" s="49">
+      <c r="C19" s="49">
         <f>SUMIFS('Оснащение и офис'!J5:J181,'Оснащение и офис'!A5:A181,"Прочие")</f>
         <v>9400000</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D19" s="50">
         <f t="shared" si="0"/>
         <v>783333.33333333337</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="55">
-        <f>B8+B9+B10+B11+B12+B13+B14+B17+B18+B20</f>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="55">
+        <f>B7+B8+B9+B10+B11+B12+B13+B16+B17+B19</f>
         <v>195716094.90860218</v>
       </c>
-      <c r="C21" s="55">
-        <f>C8+C9+C10+C11+C12+C13+C14+C17+C18+C20</f>
+      <c r="C20" s="55">
+        <f>C7+C8+C9+C10+C11+C12+C13+C16+C17+C19</f>
         <v>856341903.79166663</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D20" s="56">
         <f t="shared" si="0"/>
         <v>71361825.315972224</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B22" s="49">
-        <f>B21*Резерв</f>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="49">
+        <f>B20*Резерв</f>
         <v>19571609.49086022</v>
       </c>
-      <c r="C22" s="49">
-        <f>C21*Резерв</f>
+      <c r="C21" s="49">
+        <f>C20*Резерв</f>
         <v>85634190.379166663</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D21" s="50">
         <f t="shared" si="0"/>
         <v>7136182.5315972222</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="57">
-        <f>B21+B22</f>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="57">
+        <f>B20+B21</f>
         <v>215287704.3994624</v>
       </c>
-      <c r="C23" s="57">
-        <f>C21+C22</f>
+      <c r="C22" s="57">
+        <f>C20+C21</f>
         <v>941976094.17083335</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D22" s="58">
         <f t="shared" si="0"/>
         <v>78498007.847569451</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="49">
-        <f>B23*НДС</f>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="49">
+        <f>B22*НДС</f>
         <v>34446032.703913987</v>
       </c>
-      <c r="C24" s="49">
-        <f>C23*НДС</f>
+      <c r="C23" s="49">
+        <f>C22*НДС</f>
         <v>150716175.06733334</v>
       </c>
-      <c r="D24" s="50">
+      <c r="D23" s="50">
         <f t="shared" si="0"/>
         <v>12559681.255611112</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="59">
-        <f>B23+B24</f>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="59">
+        <f>B22+B23</f>
         <v>249733737.10337639</v>
       </c>
-      <c r="C25" s="60">
-        <f>C23+C24</f>
+      <c r="C24" s="60">
+        <f>C22+C23</f>
         <v>1092692269.2381668</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D24" s="56">
         <f t="shared" si="0"/>
         <v>91057689.103180572</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="62">
-        <f>B25+C25</f>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="62">
+        <f>B24+C24</f>
         <v>1342426006.3415432</v>
       </c>
+      <c r="D25" s="48"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>476</v>
+      </c>
+      <c r="B26" s="63" t="s">
+        <v>511</v>
+      </c>
+      <c r="C26" s="64">
+        <f>B18+C18</f>
+        <v>1743000000</v>
+      </c>
       <c r="D26" s="48"/>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
-        <v>478</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>513</v>
-      </c>
-      <c r="C27" s="64">
-        <f>B19+C19</f>
-        <v>1743000000</v>
-      </c>
-      <c r="D27" s="48"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>14</v>
+      <c r="A28" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>531</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B33" s="49">
+        <f>Аренда_мес</f>
+        <v>9856200</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="B34" s="49">
-        <f>Аренда_мес</f>
-        <v>9856200</v>
+        <v>314</v>
+      </c>
+      <c r="B34" s="55">
+        <f>Аренда_с_НДС</f>
+        <v>11433192</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B35" s="55">
-        <f>Аренда_с_НДС</f>
-        <v>11433192</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B36" s="49">
+        <v>315</v>
+      </c>
+      <c r="B35" s="49">
         <f>Аренда_депозит</f>
         <v>9856200</v>
       </c>
     </row>
+    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B36" s="49">
+        <f>Аренда_мес-4909152.1</f>
+        <v>4947047.9000000004</v>
+      </c>
+    </row>
     <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>532</v>
+        <v>430</v>
       </c>
       <c r="B37" s="49">
-        <f>Аренда_мес-4909152.1</f>
-        <v>4947047.9000000004</v>
+        <f>Аренда_мес-5000000</f>
+        <v>4856200</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B38" s="49">
-        <f>Аренда_мес-5000000</f>
-        <v>4856200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="B39" s="49">
         <f>(5000000-Коммун_мес-Парковка_мест*Парковка_цена)/Площадь_офиса</f>
         <v>7609.4235100748765</v>
       </c>
     </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B39" s="49">
+        <f>'Оснащение и офис'!I13</f>
+        <v>360000</v>
+      </c>
+    </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" s="49">
-        <f>'Оснащение и офис'!I13</f>
-        <v>360000</v>
+        <f>'Оснащение и офис'!E14</f>
+        <v>841000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="B41" s="49">
-        <f>'Оснащение и офис'!E14</f>
-        <v>841000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B42" s="49">
         <f>Канцелярия!F22</f>
         <v>240750</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B43" s="49">
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B42" s="49">
         <f>SUM('Оснащение и офис'!I20:I23)</f>
         <v>182213</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
+    <row r="44" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="66" t="s">
+        <v>533</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>534</v>
+      </c>
+      <c r="C45" s="75" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="66" t="s">
+      <c r="D45" s="67" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="68" t="s">
         <v>536</v>
       </c>
-      <c r="B46" s="67" t="s">
+      <c r="B46" s="74" t="s">
         <v>537</v>
       </c>
-      <c r="C46" s="75" t="s">
+      <c r="C46" s="76" t="s">
         <v>538</v>
       </c>
-      <c r="D46" s="67" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="D46" s="69"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="68" t="s">
         <v>539</v>
       </c>
-      <c r="B47" s="74" t="s">
-        <v>540</v>
-      </c>
-      <c r="C47" s="76" t="s">
-        <v>541</v>
-      </c>
-      <c r="D47" s="69"/>
+      <c r="B47" s="70">
+        <v>309.7</v>
+      </c>
+      <c r="C47" s="77">
+        <v>469.34</v>
+      </c>
+      <c r="D47" s="70">
+        <f>C47-B47</f>
+        <v>159.63999999999999</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="68" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B48" s="70">
-        <v>309.7</v>
+        <v>340.67</v>
       </c>
       <c r="C48" s="77">
-        <v>469.34</v>
+        <v>657.08</v>
       </c>
       <c r="D48" s="70">
         <f>C48-B48</f>
-        <v>159.63999999999999</v>
+        <v>316.41000000000003</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="68" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B49" s="70">
-        <v>340.67</v>
+        <v>8.3702702702702698</v>
       </c>
       <c r="C49" s="77">
-        <v>657.08</v>
+        <v>12.684864864864901</v>
       </c>
       <c r="D49" s="70">
         <f>C49-B49</f>
-        <v>316.41000000000003</v>
+        <v>4.3145945945946309</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="68" t="s">
-        <v>544</v>
-      </c>
-      <c r="B50" s="70">
-        <v>8.3702702702702698</v>
-      </c>
-      <c r="C50" s="77">
-        <v>12.684864864864901</v>
-      </c>
-      <c r="D50" s="70">
+        <v>542</v>
+      </c>
+      <c r="B50" s="71">
+        <v>13500</v>
+      </c>
+      <c r="C50" s="78">
+        <v>15000</v>
+      </c>
+      <c r="D50" s="71">
         <f>C50-B50</f>
-        <v>4.3145945945946309</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="68" t="s">
+        <v>543</v>
+      </c>
+      <c r="B51" s="71">
+        <v>230107.1</v>
+      </c>
+      <c r="C51" s="78" t="s">
+        <v>544</v>
+      </c>
+      <c r="D51" s="71"/>
+    </row>
+    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="68" t="s">
         <v>545</v>
       </c>
-      <c r="B51" s="71">
-        <v>13500</v>
-      </c>
-      <c r="C51" s="78">
-        <v>15000</v>
-      </c>
-      <c r="D51" s="71">
-        <f>C51-B51</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="68" t="s">
+      <c r="B52" s="71">
+        <v>80000</v>
+      </c>
+      <c r="C52" s="78" t="s">
         <v>546</v>
       </c>
-      <c r="B52" s="71">
-        <v>230107.1</v>
-      </c>
-      <c r="C52" s="78" t="s">
+      <c r="D52" s="71"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="68" t="s">
         <v>547</v>
       </c>
-      <c r="D52" s="71"/>
-    </row>
-    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="68" t="s">
-        <v>548</v>
-      </c>
       <c r="B53" s="71">
-        <v>80000</v>
-      </c>
-      <c r="C53" s="78" t="s">
-        <v>549</v>
-      </c>
-      <c r="D53" s="71"/>
+        <v>4909152.0999999996</v>
+      </c>
+      <c r="C53" s="78">
+        <v>9856200</v>
+      </c>
+      <c r="D53" s="71">
+        <f t="shared" ref="D53:D62" si="1">C53-B53</f>
+        <v>4947047.9000000004</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="68" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B54" s="71">
-        <v>4909152.0999999996</v>
+        <v>5694616.4359999998</v>
       </c>
       <c r="C54" s="78">
-        <v>9856200</v>
+        <v>11433192</v>
       </c>
       <c r="D54" s="71">
-        <f t="shared" ref="D54:D63" si="1">C54-B54</f>
-        <v>4947047.9000000004</v>
+        <f t="shared" si="1"/>
+        <v>5738575.5640000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="68" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B55" s="71">
-        <v>5694616.4359999998</v>
+        <v>68335397.231999993</v>
       </c>
       <c r="C55" s="78">
-        <v>11433192</v>
+        <v>137198304</v>
       </c>
       <c r="D55" s="71">
         <f t="shared" si="1"/>
-        <v>5738575.5640000002</v>
+        <v>68862906.768000007</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="68" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B56" s="71">
-        <v>68335397.231999993</v>
+        <v>-90847.900000000402</v>
       </c>
       <c r="C56" s="78">
-        <v>137198304</v>
+        <v>4856200</v>
       </c>
       <c r="D56" s="71">
         <f t="shared" si="1"/>
-        <v>68862906.768000007</v>
+        <v>4947047.9000000004</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="68" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B57" s="71">
-        <v>-90847.900000000402</v>
+        <v>11560261.396774201</v>
       </c>
       <c r="C57" s="78">
-        <v>4856200</v>
+        <v>23209761.290322602</v>
       </c>
       <c r="D57" s="71">
         <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
+        <v>11649499.893548401</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="68" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B58" s="71">
-        <v>11560261.396774201</v>
+        <v>58909825.200000003</v>
       </c>
       <c r="C58" s="78">
-        <v>23209761.290322602</v>
+        <v>118274400</v>
       </c>
       <c r="D58" s="71">
         <f t="shared" si="1"/>
-        <v>11649499.893548401</v>
+        <v>59364574.799999997</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="68" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B59" s="71">
-        <v>58909825.200000003</v>
+        <v>4909152.0999999996</v>
       </c>
       <c r="C59" s="78">
-        <v>118274400</v>
+        <v>9856200</v>
       </c>
       <c r="D59" s="71">
         <f t="shared" si="1"/>
-        <v>59364574.799999997</v>
+        <v>4947047.9000000004</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="68" t="s">
-        <v>556</v>
-      </c>
-      <c r="B60" s="71">
-        <v>4909152.0999999996</v>
-      </c>
-      <c r="C60" s="78">
-        <v>9856200</v>
-      </c>
-      <c r="D60" s="71">
+      <c r="A60" s="72" t="s">
+        <v>554</v>
+      </c>
+      <c r="B60" s="73">
+        <v>228556542.11880901</v>
+      </c>
+      <c r="C60" s="79">
+        <v>249733737.103376</v>
+      </c>
+      <c r="D60" s="73">
         <f t="shared" si="1"/>
-        <v>4947047.9000000004</v>
+        <v>21177194.984566987</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B61" s="73">
-        <v>228556542.11880901</v>
+        <v>1016943071.79337</v>
       </c>
       <c r="C61" s="79">
-        <v>249733737.103376</v>
+        <v>1092692269.2381699</v>
       </c>
       <c r="D61" s="73">
         <f t="shared" si="1"/>
-        <v>21177194.984566987</v>
+        <v>75749197.4447999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B62" s="73">
-        <v>1016943071.79337</v>
+        <v>1245499613.9121799</v>
       </c>
       <c r="C62" s="79">
-        <v>1092692269.2381699</v>
+        <v>1342426006.3415401</v>
       </c>
       <c r="D62" s="73">
         <f t="shared" si="1"/>
-        <v>75749197.4447999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="72" t="s">
+        <v>96926392.429360151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="80" t="s">
+        <v>558</v>
+      </c>
+      <c r="B65" s="80"/>
+      <c r="C65" s="80"/>
+      <c r="D65" s="80"/>
+    </row>
+    <row r="66" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="80" t="s">
         <v>559</v>
-      </c>
-      <c r="B63" s="73">
-        <v>1245499613.9121799</v>
-      </c>
-      <c r="C63" s="79">
-        <v>1342426006.3415401</v>
-      </c>
-      <c r="D63" s="73">
-        <f t="shared" si="1"/>
-        <v>96926392.429360151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="80" t="s">
-        <v>561</v>
       </c>
       <c r="B66" s="80"/>
       <c r="C66" s="80"/>
       <c r="D66" s="80"/>
     </row>
-    <row r="67" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="80" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B67" s="80"/>
       <c r="C67" s="80"/>
@@ -3345,35 +3352,27 @@
     </row>
     <row r="68" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="80" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B68" s="80"/>
       <c r="C68" s="80"/>
       <c r="D68" s="80"/>
     </row>
-    <row r="69" spans="1:4" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="80" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B69" s="80"/>
       <c r="C69" s="80"/>
       <c r="D69" s="80"/>
     </row>
-    <row r="70" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="80" t="s">
-        <v>565</v>
-      </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
-    </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A66:D66"/>
     <mergeCell ref="A67:D67"/>
     <mergeCell ref="A68:D68"/>
     <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3392,7 +3391,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3400,573 +3399,573 @@
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" s="11">
         <v>85000</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="11">
         <v>4325</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="11">
         <v>0.06</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11">
         <v>0.05</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="11">
         <v>0.03</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" s="11">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="11">
         <v>0.1</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="11">
         <v>0.02</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="11">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="11">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="11">
         <v>200000</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="11">
         <v>28000</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="11">
         <v>530</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="11">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="11">
         <v>90000</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11">
         <v>30000</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="11">
         <v>15000</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" s="11">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B24" s="11">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B25" s="11">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП*Дней_РК+Трансп_РК</f>
         <v>190950</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B26" s="11">
         <f>Трансп_РК+Сут_РК*МРП</f>
         <v>23650</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="11">
         <v>900</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B28" s="11">
         <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B29" s="11">
         <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B31" s="11">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" s="11">
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B33" s="11">
         <f>(Авиа_межд+Отель_межд*Ночей_межд+Сут_межд*Дней_межд+Страх_межд)*Курс</f>
         <v>1219000</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="11">
         <f>Площадь_офиса*Ставка_аренды_м2+Коммун_мес+Парковка_мест*Парковка_цена</f>
         <v>9856200</v>
       </c>
       <c r="C34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B35" s="11">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B36" s="11">
         <v>0.1</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B37" s="11">
         <v>0.16</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B43">
         <f>МРП*(1+Индекс_МРП_2027)</f>
         <v>4627.75</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B44">
         <f>Авиа_РК+Отель_РК*Ночей_РК+Сут_РК*МРП_2027*Дней_РК+Трансп_РК</f>
         <v>192766.5</v>
       </c>
       <c r="C44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B45">
         <f>Трансп_РК+Сут_РК*МРП_2027</f>
         <v>24255.5</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B48" s="16">
         <f>ROUND((244.37+93.3+53.43+45.85+12.39+11.2+8.8)*1.4,2)</f>
         <v>657.08</v>
       </c>
       <c r="C48" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B49" s="5">
         <v>15000</v>
       </c>
       <c r="C49" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B50" s="5">
         <v>0</v>
       </c>
       <c r="C50" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B51" s="5">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B52" s="5">
         <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B53" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>11433192</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B54" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>9856200</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B55" s="19">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C55" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B57" s="18">
         <v>0.1</v>
       </c>
       <c r="C57" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B58" s="19">
         <f>Аренда_мес_2026</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C58" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3994,80 +3993,80 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="W4" s="4"/>
     </row>
@@ -4076,19 +4075,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D5" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>116</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>118</v>
       </c>
       <c r="G5" s="20">
         <v>1</v>
@@ -4148,7 +4147,7 @@
         <v>29319680</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4156,19 +4155,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>434</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>436</v>
-      </c>
       <c r="D6" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G6" s="20">
         <v>1</v>
@@ -4228,7 +4227,7 @@
         <v>25742720</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4236,19 +4235,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G7" s="20">
         <v>1</v>
@@ -4308,7 +4307,7 @@
         <v>25742720</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4316,19 +4315,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G8" s="20">
         <v>1</v>
@@ -4388,7 +4387,7 @@
         <v>25742720</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4396,19 +4395,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G9" s="24">
         <v>1</v>
@@ -4468,7 +4467,7 @@
         <v>23954240</v>
       </c>
       <c r="V9" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4476,19 +4475,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G10" s="20">
         <v>1</v>
@@ -4548,7 +4547,7 @@
         <v>18588800</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4556,19 +4555,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G11" s="24">
         <v>1</v>
@@ -4628,7 +4627,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V11" s="24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4636,19 +4635,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G12" s="24">
         <v>1</v>
@@ -4708,7 +4707,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4716,19 +4715,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13" s="24">
         <v>1</v>
@@ -4788,7 +4787,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V13" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4796,19 +4795,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="D14" s="25" t="s">
         <v>444</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>446</v>
-      </c>
       <c r="E14" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G14" s="24">
         <v>1</v>
@@ -4868,7 +4867,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V14" s="24" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4876,19 +4875,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G15" s="24">
         <v>1</v>
@@ -4948,7 +4947,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V15" s="24" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4956,19 +4955,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G16" s="24">
         <v>1</v>
@@ -5028,7 +5027,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V16" s="24" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5036,19 +5035,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G17" s="24">
         <v>1</v>
@@ -5108,7 +5107,7 @@
         <v>21958053.333333332</v>
       </c>
       <c r="V17" s="24" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5116,19 +5115,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G18" s="20">
         <v>1</v>
@@ -5188,7 +5187,7 @@
         <v>20377280</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5196,19 +5195,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>384</v>
-      </c>
       <c r="D19" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G19" s="20">
         <v>1</v>
@@ -5268,7 +5267,7 @@
         <v>18588800</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5276,19 +5275,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>384</v>
-      </c>
       <c r="D20" s="25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G20" s="24">
         <v>1</v>
@@ -5348,7 +5347,7 @@
         <v>17039733.333333332</v>
       </c>
       <c r="V20" s="24" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5356,19 +5355,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>384</v>
-      </c>
       <c r="D21" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G21" s="20">
         <v>1</v>
@@ -5428,7 +5427,7 @@
         <v>18588800</v>
       </c>
       <c r="V21" s="20" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5436,19 +5435,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G22" s="20">
         <v>1</v>
@@ -5508,7 +5507,7 @@
         <v>18588800</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5516,19 +5515,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G23" s="20">
         <v>1</v>
@@ -5588,7 +5587,7 @@
         <v>13223360</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5596,19 +5595,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G24" s="24">
         <v>1</v>
@@ -5668,7 +5667,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V24" s="24" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5676,19 +5675,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G25" s="24">
         <v>1</v>
@@ -5748,7 +5747,7 @@
         <v>12121413.333333332</v>
       </c>
       <c r="V25" s="24" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5756,19 +5755,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="24">
         <v>1</v>
@@ -5828,7 +5827,7 @@
         <v>13760853.333333334</v>
       </c>
       <c r="V26" s="24" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5836,19 +5835,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G27" s="20">
         <v>1</v>
@@ -5908,7 +5907,7 @@
         <v>23954240</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5916,19 +5915,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="E28" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="C28" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>377</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>393</v>
-      </c>
       <c r="F28" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G28" s="28">
         <v>0</v>
@@ -5988,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5996,19 +5995,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G29" s="20">
         <v>1</v>
@@ -6068,7 +6067,7 @@
         <v>23954240</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6076,19 +6075,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G30" s="20">
         <v>1</v>
@@ -6148,7 +6147,7 @@
         <v>18588800</v>
       </c>
       <c r="V30" s="20" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6156,19 +6155,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G31" s="28">
         <v>0</v>
@@ -6228,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="28" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6236,19 +6235,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G32" s="28">
         <v>0</v>
@@ -6308,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6316,19 +6315,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G33" s="28">
         <v>0</v>
@@ -6388,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="28" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6396,19 +6395,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G34" s="20">
         <v>1</v>
@@ -6468,7 +6467,7 @@
         <v>18588800</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6476,19 +6475,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G35" s="20">
         <v>1</v>
@@ -6548,7 +6547,7 @@
         <v>13223360</v>
       </c>
       <c r="V35" s="20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6556,19 +6555,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G36" s="28">
         <v>0</v>
@@ -6628,7 +6627,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="28" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6636,19 +6635,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G37" s="20">
         <v>1</v>
@@ -6708,7 +6707,7 @@
         <v>25742720</v>
       </c>
       <c r="V37" s="20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6716,19 +6715,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G38" s="20">
         <v>1</v>
@@ -6788,7 +6787,7 @@
         <v>13223360</v>
       </c>
       <c r="V38" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6796,19 +6795,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G39" s="20">
         <v>1</v>
@@ -6868,7 +6867,7 @@
         <v>22165760</v>
       </c>
       <c r="V39" s="20" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6876,19 +6875,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G40" s="28">
         <v>0</v>
@@ -6948,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="28" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6956,19 +6955,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G41" s="28">
         <v>0</v>
@@ -7028,14 +7027,14 @@
         <v>0</v>
       </c>
       <c r="V41" s="28" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="C42" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -7092,7 +7091,7 @@
     </row>
     <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G43">
         <f>SUM(G8:G13)+SUM(G17:G36)</f>
@@ -7105,7 +7104,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G44">
         <f>SUM(G5:G7)+SUM(G14:G16)+SUM(G37:G41)</f>
@@ -7142,42 +7141,42 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>480</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="G3" s="33" t="s">
         <v>481</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>482</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>483</v>
-      </c>
       <c r="H3" s="33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L3" s="33">
         <v>2027</v>
@@ -7188,13 +7187,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E4" s="36">
         <v>1000000</v>
@@ -7232,13 +7231,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E5" s="36">
         <v>700000</v>
@@ -7276,13 +7275,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>488</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>490</v>
       </c>
       <c r="E6" s="36">
         <v>1000000</v>
@@ -7320,13 +7319,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>491</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>492</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>493</v>
       </c>
       <c r="E7" s="36">
         <v>1000000</v>
@@ -7364,13 +7363,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E8" s="36">
         <v>700000</v>
@@ -7408,13 +7407,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E9" s="36">
         <v>700000</v>
@@ -7452,13 +7451,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E10" s="36">
         <v>700000</v>
@@ -7494,7 +7493,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="38"/>
       <c r="B11" s="38" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -7543,41 +7542,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -7795,7 +7794,7 @@
     </row>
     <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G9:G13)</f>
@@ -7829,7 +7828,7 @@
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C12">
         <f>SUM(Штат!G17:G26)</f>
@@ -7863,7 +7862,7 @@
     </row>
     <row r="13" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C13">
         <f>SUM(Штат!G14:G16)</f>
@@ -7897,7 +7896,7 @@
     </row>
     <row r="14" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C14">
         <f>SUM(Штат!G27:G28)</f>
@@ -7931,7 +7930,7 @@
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C15">
         <f>SUM(Штат!G29:G36)</f>
@@ -8105,7 +8104,7 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -8148,41 +8147,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J4" s="3">
         <v>2027</v>
@@ -8190,13 +8189,13 @@
     </row>
     <row r="5" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
         <v>140</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" t="s">
-        <v>142</v>
       </c>
       <c r="D5" s="12">
         <v>25</v>
@@ -8205,13 +8204,13 @@
         <v>450000</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G5" s="12">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I38" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -8224,13 +8223,13 @@
     </row>
     <row r="6" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" t="s">
-        <v>142</v>
       </c>
       <c r="D6" s="12">
         <v>5</v>
@@ -8239,13 +8238,13 @@
         <v>900000</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G6" s="12">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -8258,13 +8257,13 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D7" s="12">
         <v>15</v>
@@ -8273,13 +8272,13 @@
         <v>100000</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G7" s="12">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -8292,13 +8291,13 @@
     </row>
     <row r="8" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D8" s="12">
         <v>19</v>
@@ -8307,13 +8306,13 @@
         <v>200000</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -8326,13 +8325,13 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="12">
         <v>5</v>
@@ -8341,13 +8340,13 @@
         <v>500000</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G9" s="12">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
@@ -8360,13 +8359,13 @@
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
@@ -8375,7 +8374,7 @@
         <v>800000</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
@@ -8392,13 +8391,13 @@
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
@@ -8407,7 +8406,7 @@
         <v>500000</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G11" s="12">
         <v>1</v>
@@ -8424,13 +8423,13 @@
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -8439,13 +8438,13 @@
         <v>450000</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G12" s="12">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -8458,13 +8457,13 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" t="s">
         <v>140</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C13" t="s">
-        <v>142</v>
       </c>
       <c r="D13" s="12">
         <v>6</v>
@@ -8473,13 +8472,13 @@
         <v>60000</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G13" s="12">
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
@@ -8492,13 +8491,13 @@
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -8508,13 +8507,13 @@
         <v>841000</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G14" s="12">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
@@ -8527,13 +8526,13 @@
     </row>
     <row r="15" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" t="s">
         <v>140</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" t="s">
-        <v>142</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
@@ -8542,13 +8541,13 @@
         <v>2500000</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G15" s="12">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
@@ -8561,13 +8560,13 @@
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -8576,7 +8575,7 @@
         <v>300000</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G16" s="12">
         <v>1</v>
@@ -8593,13 +8592,13 @@
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" t="s">
         <v>140</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C17" t="s">
-        <v>142</v>
       </c>
       <c r="D17" s="12">
         <v>2</v>
@@ -8608,13 +8607,13 @@
         <v>280000</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
@@ -8627,13 +8626,13 @@
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" t="s">
         <v>140</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C18" t="s">
-        <v>142</v>
       </c>
       <c r="D18" s="12">
         <v>4</v>
@@ -8642,13 +8641,13 @@
         <v>55000</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="12">
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
@@ -8661,13 +8660,13 @@
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -8676,13 +8675,13 @@
         <v>300000</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G19" s="12">
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
@@ -8695,13 +8694,13 @@
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C20" t="s">
         <v>140</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C20" t="s">
-        <v>142</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -8711,13 +8710,13 @@
         <v>36500</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G20" s="12">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
@@ -8730,13 +8729,13 @@
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C21" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -8746,13 +8745,13 @@
         <v>5172</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G21" s="12">
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
@@ -8765,13 +8764,13 @@
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" t="s">
         <v>140</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C22" t="s">
-        <v>142</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -8781,13 +8780,13 @@
         <v>98558</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G22" s="12">
         <v>1</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="0"/>
@@ -8800,13 +8799,13 @@
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -8816,13 +8815,13 @@
         <v>41983</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G23" s="12">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="0"/>
@@ -8835,13 +8834,13 @@
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C24" t="s">
         <v>140</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C24" t="s">
-        <v>142</v>
       </c>
       <c r="D24" s="12">
         <v>31</v>
@@ -8851,13 +8850,13 @@
         <v>3550</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G24" s="12">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -8870,13 +8869,13 @@
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C25" t="s">
         <v>140</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C25" t="s">
-        <v>142</v>
       </c>
       <c r="D25" s="12">
         <v>5</v>
@@ -8886,13 +8885,13 @@
         <v>5259</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G25" s="12">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -8905,13 +8904,13 @@
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C26" t="s">
         <v>140</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="C26" t="s">
-        <v>142</v>
       </c>
       <c r="D26" s="12">
         <v>4</v>
@@ -8921,13 +8920,13 @@
         <v>6237</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G26" s="12">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -8940,13 +8939,13 @@
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C27" t="s">
         <v>140</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="C27" t="s">
-        <v>142</v>
       </c>
       <c r="D27" s="12">
         <v>5</v>
@@ -8956,13 +8955,13 @@
         <v>7792</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G27" s="12">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="0"/>
@@ -8975,13 +8974,13 @@
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="C28" t="s">
         <v>140</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="C28" t="s">
-        <v>142</v>
       </c>
       <c r="D28" s="12">
         <v>10</v>
@@ -8991,13 +8990,13 @@
         <v>76984</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G28" s="12">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" ref="I28" si="2">IF(F28="разово",IF(G28&lt;=3,D28*E28,0),IF(F28="мес",D28*E28*MAX(0,4-G28),D28*E28*MAX(0,4-G28)/12))</f>
@@ -9010,13 +9009,13 @@
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" t="s">
         <v>140</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" t="s">
-        <v>142</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
@@ -9025,13 +9024,13 @@
         <v>450000</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="0"/>
@@ -9044,13 +9043,13 @@
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C30" t="s">
         <v>140</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C30" t="s">
-        <v>142</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
@@ -9060,13 +9059,13 @@
         <v>49872</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -9079,13 +9078,13 @@
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -9094,13 +9093,13 @@
         <v>300000</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -9113,13 +9112,13 @@
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -9128,13 +9127,13 @@
         <v>800000</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G32" s="12">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
@@ -9147,13 +9146,13 @@
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C33" t="s">
         <v>140</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" t="s">
-        <v>142</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -9162,7 +9161,7 @@
         <v>700000</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G33" s="12">
         <v>1</v>
@@ -9179,13 +9178,13 @@
     </row>
     <row r="34" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -9195,13 +9194,13 @@
         <v>7062880</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -9214,13 +9213,13 @@
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -9229,7 +9228,7 @@
         <v>400000</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G35" s="12">
         <v>1</v>
@@ -9246,13 +9245,13 @@
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -9261,7 +9260,7 @@
         <v>150000</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G36" s="12">
         <v>1</v>
@@ -9278,13 +9277,13 @@
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -9293,7 +9292,7 @@
         <v>400000</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -9310,13 +9309,13 @@
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
@@ -9325,13 +9324,13 @@
         <v>100000</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G38" s="12">
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
@@ -9344,13 +9343,13 @@
     </row>
     <row r="39" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" t="s">
         <v>168</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" t="s">
-        <v>170</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -9360,13 +9359,13 @@
         <v>9856200</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G39" s="12">
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I39" s="5">
         <f>D39*E39*Аренда_мес_2026</f>
@@ -9379,13 +9378,13 @@
     </row>
     <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
@@ -9395,13 +9394,13 @@
         <v>9856200</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G40" s="12">
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" ref="I40:I66" si="5">IF(F40="разово",IF(G40&lt;=3,D40*E40,0),IF(F40="мес",D40*E40*MAX(0,4-G40),D40*E40*MAX(0,4-G40)/12))</f>
@@ -9414,13 +9413,13 @@
     </row>
     <row r="41" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -9429,13 +9428,13 @@
         <v>3000000</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" si="5"/>
@@ -9448,13 +9447,13 @@
     </row>
     <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" t="s">
         <v>168</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42" t="s">
-        <v>170</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -9463,7 +9462,7 @@
         <v>50000</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G42" s="12">
         <v>1</v>
@@ -9480,13 +9479,13 @@
     </row>
     <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C43" t="s">
         <v>168</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43" t="s">
-        <v>170</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -9495,7 +9494,7 @@
         <v>60000</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G43" s="12">
         <v>1</v>
@@ -9512,13 +9511,13 @@
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" t="s">
         <v>168</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C44" t="s">
-        <v>170</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -9527,7 +9526,7 @@
         <v>50000</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G44" s="12">
         <v>1</v>
@@ -9544,13 +9543,13 @@
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D45" s="12">
         <v>25</v>
@@ -9559,13 +9558,13 @@
         <v>5000</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G45" s="12">
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="5"/>
@@ -9578,13 +9577,13 @@
     </row>
     <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C46" t="s">
         <v>168</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C46" t="s">
-        <v>170</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -9593,7 +9592,7 @@
         <v>60000</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G46" s="12">
         <v>1</v>
@@ -9610,13 +9609,13 @@
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47" t="s">
         <v>168</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" t="s">
-        <v>170</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -9626,13 +9625,13 @@
         <v>240750</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="5"/>
@@ -9645,13 +9644,13 @@
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C48" t="s">
         <v>168</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C48" t="s">
-        <v>170</v>
       </c>
       <c r="D48" s="12">
         <v>0</v>
@@ -9660,13 +9659,13 @@
         <v>200000</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="5"/>
@@ -9679,13 +9678,13 @@
     </row>
     <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C49" t="s">
         <v>168</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" t="s">
-        <v>170</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -9694,7 +9693,7 @@
         <v>150000</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G49" s="12">
         <v>1</v>
@@ -9711,13 +9710,13 @@
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" t="s">
         <v>168</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C50" t="s">
-        <v>170</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -9726,7 +9725,7 @@
         <v>100000</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G50" s="12">
         <v>1</v>
@@ -9743,13 +9742,13 @@
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" t="s">
         <v>186</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C51" t="s">
-        <v>188</v>
       </c>
       <c r="D51" s="12">
         <v>25</v>
@@ -9758,13 +9757,13 @@
         <v>7000</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G51" s="12">
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="5"/>
@@ -9777,13 +9776,13 @@
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" t="s">
         <v>186</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" t="s">
-        <v>188</v>
       </c>
       <c r="D52" s="12">
         <v>3</v>
@@ -9792,7 +9791,7 @@
         <v>7500</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -9809,13 +9808,13 @@
     </row>
     <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D53" s="12">
         <v>2</v>
@@ -9824,13 +9823,13 @@
         <v>30000</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G53" s="12">
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="5"/>
@@ -9843,13 +9842,13 @@
     </row>
     <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D54" s="12">
         <v>2</v>
@@ -9858,7 +9857,7 @@
         <v>8000</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -9875,13 +9874,13 @@
     </row>
     <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -9890,13 +9889,13 @@
         <v>200000</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G55" s="12">
         <v>4</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="5"/>
@@ -9909,13 +9908,13 @@
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D56" s="12">
         <v>1</v>
@@ -9924,13 +9923,13 @@
         <v>300000</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G56" s="12">
         <v>4</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="5"/>
@@ -9943,18 +9942,18 @@
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C57" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="13"/>
       <c r="F57" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G57" s="12"/>
       <c r="H57" s="4"/>
@@ -9967,13 +9966,13 @@
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>196</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" t="s">
         <v>198</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C58" t="s">
-        <v>200</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -9982,7 +9981,7 @@
         <v>5000000</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G58" s="12">
         <v>1</v>
@@ -9999,13 +9998,13 @@
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -10014,7 +10013,7 @@
         <v>25000</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -10031,13 +10030,13 @@
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>196</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" t="s">
         <v>198</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" t="s">
-        <v>200</v>
       </c>
       <c r="D60" s="12">
         <v>0</v>
@@ -10046,13 +10045,13 @@
         <v>10000000</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G60" s="12">
         <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="5"/>
@@ -10065,13 +10064,13 @@
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" t="s">
         <v>203</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" t="s">
-        <v>205</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
@@ -10080,13 +10079,13 @@
         <v>700000</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="5"/>
@@ -10099,13 +10098,13 @@
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D62" s="12">
         <v>25</v>
@@ -10114,7 +10113,7 @@
         <v>150000</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G62" s="12">
         <v>1</v>
@@ -10131,13 +10130,13 @@
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C63" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -10146,7 +10145,7 @@
         <v>2000000</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G63" s="12">
         <v>1</v>
@@ -10163,13 +10162,13 @@
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D64" s="12">
         <v>2</v>
@@ -10178,7 +10177,7 @@
         <v>3000000</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G64" s="12">
         <v>0</v>
@@ -10193,13 +10192,13 @@
     </row>
     <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -10208,7 +10207,7 @@
         <v>500000</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -10225,13 +10224,13 @@
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
@@ -10240,7 +10239,7 @@
         <v>150000</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -10281,7 +10280,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -10289,25 +10288,25 @@
     </row>
     <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3">
         <v>2027</v>
@@ -10315,18 +10314,18 @@
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
       <c r="F5" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G5" s="5">
         <v>6000000</v>
@@ -10337,18 +10336,18 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13"/>
       <c r="F6" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G6" s="5">
         <v>2000000</v>
@@ -10359,18 +10358,18 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>474</v>
-      </c>
       <c r="C7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="13"/>
       <c r="F7" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G7" s="5">
         <v>10000000</v>
@@ -10381,18 +10380,18 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="13"/>
       <c r="F8" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -10403,18 +10402,18 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
       <c r="F9" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -10425,18 +10424,18 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="13"/>
       <c r="F10" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -10447,18 +10446,18 @@
     </row>
     <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
       <c r="F11" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G11" s="5">
         <v>30000000</v>
@@ -10469,18 +10468,18 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
       <c r="F12" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G12" s="5">
         <v>15000000</v>
@@ -10491,18 +10490,18 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
       <c r="F13" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G13" s="5">
         <v>50000000</v>
@@ -10513,18 +10512,18 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
       <c r="F14" s="12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G14" s="5">
         <v>100000000</v>
@@ -10539,7 +10538,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -10556,7 +10555,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G18" s="81">
         <f>G16+H16</f>
@@ -10592,46 +10591,46 @@
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="E4" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>275</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5" t="s">
         <v>276</v>
-      </c>
-      <c r="B5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C5" t="s">
-        <v>278</v>
       </c>
       <c r="D5" s="16">
         <v>7</v>
@@ -10644,18 +10643,18 @@
         <v>21000</v>
       </c>
       <c r="G5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" t="s">
         <v>276</v>
-      </c>
-      <c r="B6" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" t="s">
-        <v>278</v>
       </c>
       <c r="D6" s="16">
         <v>0.5</v>
@@ -10668,18 +10667,18 @@
         <v>3250</v>
       </c>
       <c r="G6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D7" s="16">
         <v>1</v>
@@ -10692,18 +10691,18 @@
         <v>6000</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8" s="16">
         <v>0.5</v>
@@ -10716,18 +10715,18 @@
         <v>2500</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="16">
         <v>20</v>
@@ -10740,18 +10739,18 @@
         <v>24000</v>
       </c>
       <c r="G9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D10" s="16">
         <v>20</v>
@@ -10764,18 +10763,18 @@
         <v>18000</v>
       </c>
       <c r="G10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="16">
         <v>10</v>
@@ -10788,18 +10787,18 @@
         <v>15000</v>
       </c>
       <c r="G11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" s="16">
         <v>0.5</v>
@@ -10812,18 +10811,18 @@
         <v>4000</v>
       </c>
       <c r="G12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
@@ -10836,18 +10835,18 @@
         <v>10000</v>
       </c>
       <c r="G13" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D14" s="16">
         <v>0.5</v>
@@ -10862,13 +10861,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
@@ -10881,18 +10880,18 @@
         <v>12000</v>
       </c>
       <c r="G15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="16">
         <v>0.5</v>
@@ -10905,18 +10904,18 @@
         <v>4000</v>
       </c>
       <c r="G16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" s="16">
         <v>0.2</v>
@@ -10929,18 +10928,18 @@
         <v>5000</v>
       </c>
       <c r="G17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
@@ -10953,18 +10952,18 @@
         <v>35000</v>
       </c>
       <c r="G18" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D19" s="16">
         <v>0.2</v>
@@ -10979,13 +10978,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D20" s="16">
         <v>20</v>
@@ -10998,18 +10997,18 @@
         <v>36000</v>
       </c>
       <c r="G20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
@@ -11022,12 +11021,12 @@
         <v>40000</v>
       </c>
       <c r="G21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D22" s="41"/>
       <c r="E22" s="8"/>
@@ -11038,7 +11037,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="5"/>
@@ -11049,7 +11048,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -11083,40 +11082,40 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -11130,13 +11129,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11154,13 +11153,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -11178,13 +11177,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8">
         <v>2534</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -11202,13 +11201,13 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C9">
         <v>6218</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -11226,13 +11225,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C10">
         <v>7045</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -11250,13 +11249,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11">
         <v>4240</v>
       </c>
       <c r="D11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -11274,13 +11273,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C12">
         <v>6976</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -11298,13 +11297,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C13">
         <v>5729</v>
       </c>
       <c r="D13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -11322,13 +11321,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C14">
         <v>3288</v>
       </c>
       <c r="D14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11346,13 +11345,13 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C15">
         <v>1756</v>
       </c>
       <c r="D15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -11370,13 +11369,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C16">
         <v>4400</v>
       </c>
       <c r="D16" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -11392,7 +11391,7 @@
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -11409,7 +11408,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -11423,10 +11422,10 @@
         <v>2.1</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -11444,10 +11443,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -11465,10 +11464,10 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -11486,10 +11485,10 @@
         <v>2.4</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -11507,10 +11506,10 @@
         <v>2.5</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -11528,10 +11527,10 @@
         <v>2.6</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -11547,7 +11546,7 @@
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -11564,7 +11563,7 @@
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -11578,10 +11577,10 @@
         <v>3.1</v>
       </c>
       <c r="B29" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -11599,10 +11598,10 @@
         <v>3.2</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -11620,10 +11619,10 @@
         <v>3.3</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -11641,10 +11640,10 @@
         <v>3.4</v>
       </c>
       <c r="B32" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -11660,7 +11659,7 @@
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -11678,7 +11677,7 @@
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
